--- a/data/trans_bre/IP16B01-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP16B01-Edad-trans_bre.xlsx
@@ -639,12 +639,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-16,17; 0,0</t>
+          <t>-14,17; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-18,83; 9,12</t>
+          <t>-18,32; 9,58</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -654,12 +654,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-16,17; 0,0</t>
+          <t>-14,17; 0,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-19,65; 9,69</t>
+          <t>-19,63; 10,27</t>
         </is>
       </c>
     </row>
@@ -714,17 +714,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,74</t>
+          <t>0,0; 9,52</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-21,1; 3,73</t>
+          <t>-21,68; 2,3</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-22,34; 7,06</t>
+          <t>-23,19; 7,2</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -734,12 +734,12 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-23,05; 4,25</t>
+          <t>-22,93; 2,77</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-23,89; 8,36</t>
+          <t>-24,18; 8,57</t>
         </is>
       </c>
     </row>
@@ -799,12 +799,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-50,37; -5,26</t>
+          <t>-49,77; -3,85</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,65; 43,05</t>
+          <t>-8,64; 44,65</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -814,12 +814,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-51,92; -5,72</t>
+          <t>-52,0; -5,05</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-9,93; 92,69</t>
+          <t>-9,28; 102,62</t>
         </is>
       </c>
     </row>
@@ -879,12 +879,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-32,75; 16,61</t>
+          <t>-32,94; 15,68</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-72,7; -19,71</t>
+          <t>-69,83; -17,99</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-35,71; 23,03</t>
+          <t>-36,44; 21,15</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-72,7; -19,71</t>
+          <t>-69,83; -17,99</t>
         </is>
       </c>
     </row>
@@ -954,17 +954,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,51</t>
+          <t>0,0; 3,76</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-19,16; -3,56</t>
+          <t>-18,93; -3,9</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-16,04; 3,5</t>
+          <t>-16,11; 2,85</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-20,3; -3,97</t>
+          <t>-20,29; -4,37</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-17,48; 4,18</t>
+          <t>-17,81; 3,37</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP16B01-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP16B01-Edad-trans_bre.xlsx
@@ -639,12 +639,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-14,17; 0,0</t>
+          <t>-16,44; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-18,32; 9,58</t>
+          <t>-17,32; 10,03</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -654,12 +654,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-14,17; 0,0</t>
+          <t>-16,44; 0,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-19,63; 10,27</t>
+          <t>-20,02; 10,41</t>
         </is>
       </c>
     </row>
@@ -714,17 +714,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,52</t>
+          <t>0,0; 9,44</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-21,68; 2,3</t>
+          <t>-21,88; 3,21</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-23,19; 7,2</t>
+          <t>-23,59; 7,24</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -734,12 +734,12 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-22,93; 2,77</t>
+          <t>-23,32; 3,64</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-24,18; 8,57</t>
+          <t>-25,27; 8,74</t>
         </is>
       </c>
     </row>
@@ -799,12 +799,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-49,77; -3,85</t>
+          <t>-50,88; -5,88</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,64; 44,65</t>
+          <t>-7,51; 43,45</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -814,12 +814,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-52,0; -5,05</t>
+          <t>-52,38; -6,78</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-9,28; 102,62</t>
+          <t>-7,71; 98,83</t>
         </is>
       </c>
     </row>
@@ -879,12 +879,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-32,94; 15,68</t>
+          <t>-33,25; 16,51</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-69,83; -17,99</t>
+          <t>-73,14; -20,43</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-36,44; 21,15</t>
+          <t>-36,03; 22,01</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-69,83; -17,99</t>
+          <t>-73,14; -20,43</t>
         </is>
       </c>
     </row>
@@ -954,17 +954,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,76</t>
+          <t>0,0; 3,77</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-18,93; -3,9</t>
+          <t>-19,32; -3,78</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-16,11; 2,85</t>
+          <t>-16,29; 2,85</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-20,29; -4,37</t>
+          <t>-20,1; -4,28</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-17,81; 3,37</t>
+          <t>-18,19; 3,15</t>
         </is>
       </c>
     </row>
